--- a/task_01/testing_plan.xlsx
+++ b/task_01/testing_plan.xlsx
@@ -112,15 +112,6 @@
     <t>TC-03</t>
   </si>
   <si>
-    <t>Ask Assistant / AI Widget Test</t>
-  </si>
-  <si>
-    <t>1. Locate the "Ask AI" / Assistant trigger widget on the page.</t>
-  </si>
-  <si>
-    <t>2. Click the widget to open the chat window.</t>
-  </si>
-  <si>
     <t>3. Verify modal elements.</t>
   </si>
   <si>
@@ -335,9 +326,6 @@
     <t>User see hovering text "You cannot buy this phone number, please upgrade your account to make this available".</t>
   </si>
   <si>
-    <t>Assistant panel opens, displaying an active prompt input field. It has header "Ask our AI Assistant".</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Copyright text shows </t>
     </r>
@@ -359,6 +347,18 @@
       </rPr>
       <t>, and Privacy Policy link is not visible and clickable.</t>
     </r>
+  </si>
+  <si>
+    <t>Contact us</t>
+  </si>
+  <si>
+    <t>1. Locate the "Contact us" on the page.</t>
+  </si>
+  <si>
+    <t>2. Click the button to open page with submit form</t>
+  </si>
+  <si>
+    <t>Submit form appears on page with address "https://telnyx.com/contact-us"</t>
   </si>
 </sst>
 </file>
@@ -410,12 +410,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="7">
@@ -500,7 +506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -557,6 +563,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -864,7 +879,7 @@
     </row>
     <row r="2" spans="1:6" ht="18.75">
       <c r="A2" s="16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -874,7 +889,7 @@
     </row>
     <row r="3" spans="1:6" ht="18.75">
       <c r="A3" s="17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -911,7 +926,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="22.5" customHeight="1">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="20" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -924,14 +939,14 @@
         <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="10"/>
+      <c r="A7" s="21"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="13"/>
@@ -939,17 +954,17 @@
       <c r="F7" s="13"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="10"/>
+      <c r="A8" s="21"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="13"/>
       <c r="E8" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F8" s="13"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="10"/>
+      <c r="A9" s="21"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="D9" s="13"/>
@@ -957,24 +972,24 @@
       <c r="F9" s="13"/>
     </row>
     <row r="10" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A10" s="11"/>
+      <c r="A10" s="22"/>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="D10" s="14"/>
       <c r="E10" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F10" s="14"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="20" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>12</v>
@@ -983,11 +998,11 @@
         <v>13</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="10"/>
+      <c r="A12" s="21"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="13"/>
@@ -995,7 +1010,7 @@
       <c r="F12" s="13"/>
     </row>
     <row r="13" spans="1:6" ht="28.5">
-      <c r="A13" s="10"/>
+      <c r="A13" s="21"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="13"/>
@@ -1005,7 +1020,7 @@
       <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="10"/>
+      <c r="A14" s="21"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="13"/>
@@ -1013,7 +1028,7 @@
       <c r="F14" s="13"/>
     </row>
     <row r="15" spans="1:6" ht="29.25" thickBot="1">
-      <c r="A15" s="11"/>
+      <c r="A15" s="22"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
       <c r="D15" s="14"/>
@@ -1023,27 +1038,27 @@
       <c r="F15" s="14"/>
     </row>
     <row r="16" spans="1:6" ht="54.75" customHeight="1">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="20" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="10"/>
+      <c r="A17" s="21"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
       <c r="D17" s="13"/>
@@ -1051,17 +1066,17 @@
       <c r="F17" s="13"/>
     </row>
     <row r="18" spans="1:6" ht="28.5">
-      <c r="A18" s="10"/>
+      <c r="A18" s="21"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
       <c r="D18" s="13"/>
       <c r="E18" s="3" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="F18" s="13"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="10"/>
+      <c r="A19" s="21"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="13"/>
@@ -1069,33 +1084,33 @@
       <c r="F19" s="13"/>
     </row>
     <row r="20" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A20" s="11"/>
+      <c r="A20" s="22"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="D20" s="14"/>
       <c r="E20" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F20" s="14"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="9" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1112,7 +1127,7 @@
       <c r="C23" s="10"/>
       <c r="D23" s="13"/>
       <c r="E23" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F23" s="13"/>
     </row>
@@ -1130,7 +1145,7 @@
       <c r="C25" s="10"/>
       <c r="D25" s="13"/>
       <c r="E25" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F25" s="13"/>
     </row>
@@ -1140,28 +1155,28 @@
       <c r="C26" s="11"/>
       <c r="D26" s="14"/>
       <c r="E26" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F26" s="14"/>
     </row>
     <row r="27" spans="1:6" ht="18.75" customHeight="1">
       <c r="A27" s="9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="12" t="s">
         <v>45</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1177,7 +1192,7 @@
       <c r="C29" s="10"/>
       <c r="D29" s="13"/>
       <c r="E29" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F29" s="13"/>
     </row>
@@ -1195,28 +1210,28 @@
       <c r="C31" s="11"/>
       <c r="D31" s="14"/>
       <c r="E31" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F31" s="14"/>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1225,7 +1240,7 @@
       <c r="C33" s="10"/>
       <c r="D33" s="13"/>
       <c r="E33" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F33" s="13"/>
     </row>
@@ -1235,7 +1250,7 @@
       <c r="C34" s="10"/>
       <c r="D34" s="13"/>
       <c r="E34" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F34" s="13"/>
     </row>
@@ -1245,7 +1260,7 @@
       <c r="C35" s="10"/>
       <c r="D35" s="13"/>
       <c r="E35" s="18" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F35" s="13"/>
     </row>
@@ -1259,22 +1274,22 @@
     </row>
     <row r="37" spans="1:6" ht="28.5">
       <c r="A37" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1291,7 +1306,7 @@
       <c r="C39" s="10"/>
       <c r="D39" s="13"/>
       <c r="E39" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F39" s="13"/>
     </row>
@@ -1308,28 +1323,28 @@
       <c r="C41" s="11"/>
       <c r="D41" s="14"/>
       <c r="E41" s="8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F41" s="14"/>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1">
       <c r="A42" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E42" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F42" s="12" t="s">
         <v>62</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1346,7 +1361,7 @@
       <c r="C44" s="10"/>
       <c r="D44" s="13"/>
       <c r="E44" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F44" s="13"/>
     </row>
@@ -1364,28 +1379,28 @@
       <c r="C46" s="11"/>
       <c r="D46" s="14"/>
       <c r="E46" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F46" s="14"/>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E47" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F47" s="12" t="s">
         <v>67</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1402,7 +1417,7 @@
       <c r="C49" s="10"/>
       <c r="D49" s="13"/>
       <c r="E49" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F49" s="13"/>
     </row>
@@ -1420,28 +1435,28 @@
       <c r="C51" s="11"/>
       <c r="D51" s="14"/>
       <c r="E51" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F51" s="14"/>
     </row>
     <row r="52" spans="1:6" ht="25.5" customHeight="1">
       <c r="A52" s="9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1450,7 +1465,7 @@
       <c r="C53" s="10"/>
       <c r="D53" s="13"/>
       <c r="E53" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F53" s="13"/>
     </row>
@@ -1460,7 +1475,7 @@
       <c r="C54" s="10"/>
       <c r="D54" s="13"/>
       <c r="E54" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F54" s="13"/>
     </row>
@@ -1470,7 +1485,7 @@
       <c r="C55" s="10"/>
       <c r="D55" s="13"/>
       <c r="E55" s="8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F55" s="13"/>
     </row>
